--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FC Arges</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2193,22 +2193,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>06/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Csikszereda M. Ciuc</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Din. Bucuresti</t>
+          <t>Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Din. Bucuresti</t>
+          <t>Dinamo Bucuresti</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2251,22 +2251,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Petrolul</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2309,22 +2309,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Csikszereda M. Ciuc</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" t="n">
+        <v>17</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2367,22 +2367,62 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Unirea Slobozia</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M34" t="n">
+        <v>26</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2425,22 +2425,62 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FC Hermannstadt</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N35" t="n">
+        <v>19</v>
+      </c>
+      <c r="O35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2483,22 +2483,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>22</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2541,22 +2541,62 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>UTA Arad</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2599,22 +2599,62 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Botosani</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M38" t="n">
+        <v>22</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2657,22 +2657,62 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Otelul</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M39" t="n">
+        <v>16</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -2715,22 +2715,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Metaloglobus Bucharest</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M40" t="n">
+        <v>33</v>
+      </c>
+      <c r="N40" t="n">
+        <v>14</v>
+      </c>
+      <c r="O40" t="n">
+        <v>14</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -627,22 +627,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -685,22 +685,62 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Csikszereda M. Ciuc</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>

--- a/new-stats/fc-farul-constanta.xlsx
+++ b/new-stats/fc-farul-constanta.xlsx
@@ -743,22 +743,62 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FC Arges</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Farul Constanta</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
